--- a/Code/format_weather_profiles/pvbau_max_cap_calc.xlsx
+++ b/Code/format_weather_profiles/pvbau_max_cap_calc.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/laorie4253/Documents/MOYA Analytics/GMPA/STEVFNs/Code/format_weather_profiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{69C4A958-1D3D-8849-A87A-41478BF9C931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5826546-69E2-0649-991B-CB26051C3610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-31500" yWindow="540" windowWidth="27640" windowHeight="16760" xr2:uid="{2EB9D502-0D15-A14C-AF4C-11749A97FA38}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -202,8 +202,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FF000000"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -230,7 +230,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -820,54 +820,66 @@
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C12" s="4">
-        <v>33.68</v>
-      </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>9.6602487204368686</v>
+      </c>
+      <c r="C12" s="6">
+        <v>5.9459999999999997</v>
+      </c>
+      <c r="D12">
+        <v>252359.96200000035</v>
+      </c>
+      <c r="E12">
+        <v>410000</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="1"/>
+        <v>1.6246634242241622</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C13" s="5">
-        <v>2.2349999999999999</v>
-      </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>5.4050540979770544E-2</v>
+      </c>
+      <c r="C13" s="6">
+        <v>2.4E-2</v>
+      </c>
+      <c r="D13">
+        <v>338349.99000000086</v>
+      </c>
+      <c r="E13">
+        <v>762000</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="1"/>
+        <v>2.2521058741571061</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C14" s="5">
-        <v>72.766999999999996</v>
-      </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>15.33495559471527</v>
+      </c>
+      <c r="C14" s="6">
+        <v>5.6970000000000001</v>
+      </c>
+      <c r="D14">
+        <v>1383110.0370000005</v>
+      </c>
+      <c r="E14">
+        <v>3723000</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="1"/>
+        <v>2.6917598024776672</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -881,8 +893,6 @@
       <c r="C15" s="6">
         <v>5.3250000000000002</v>
       </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
       <c r="F15" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
@@ -1112,91 +1122,154 @@
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B26" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F26" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="B26">
+        <f t="shared" si="0"/>
+        <v>9.7946849576635682</v>
+      </c>
+      <c r="C26" s="6">
+        <v>7.1379999999999999</v>
+      </c>
+      <c r="D26">
+        <v>470051.87199999986</v>
+      </c>
+      <c r="E26">
+        <v>645000</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="1"/>
+        <v>1.3721889825810547</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B27" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F27" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="B27">
+        <f t="shared" si="0"/>
+        <v>441.97267229476751</v>
+      </c>
+      <c r="C27" s="6">
+        <v>39.223999999999997</v>
+      </c>
+      <c r="D27">
+        <v>81647.763000000356</v>
+      </c>
+      <c r="E27">
+        <v>920000</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="1"/>
+        <v>11.267914345675289</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B28" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F28" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="B28">
+        <f t="shared" si="0"/>
+        <v>33.172362873466113</v>
+      </c>
+      <c r="C28" s="6">
+        <v>24.236999999999998</v>
+      </c>
+      <c r="D28">
+        <v>4383830.0139999986</v>
+      </c>
+      <c r="E28">
+        <v>6000000</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="1"/>
+        <v>1.3686662075944265</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B29" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F29" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="B29">
+        <f t="shared" si="0"/>
+        <v>0.10976522549844003</v>
+      </c>
+      <c r="C29" s="6">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="D29">
+        <v>1055889.9640000025</v>
+      </c>
+      <c r="E29">
+        <v>1900000</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="1"/>
+        <v>1.799429926203935</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B30" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F30" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="B30">
+        <f t="shared" si="0"/>
+        <v>86.75025986275962</v>
+      </c>
+      <c r="C30" s="6">
+        <v>43.548999999999999</v>
+      </c>
+      <c r="D30">
+        <v>5796141.185000075</v>
+      </c>
+      <c r="E30">
+        <v>11546000</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="1"/>
+        <v>1.9920149684897386</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B31" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F31" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="B31">
+        <f t="shared" si="0"/>
+        <v>0.6143678145779603</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="D31">
+        <v>265720.30000000005</v>
+      </c>
+      <c r="E31">
+        <v>653000</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="1"/>
+        <v>2.4574712583118412</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B32" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F32" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="B32">
+        <f t="shared" si="0"/>
+        <v>45.747585201770271</v>
+      </c>
+      <c r="C32" s="6">
+        <v>34.15</v>
+      </c>
+      <c r="D32">
+        <v>1041350.0470000005</v>
+      </c>
+      <c r="E32">
+        <v>1395000</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="1"/>
+        <v>1.3396071801396858</v>
       </c>
     </row>
   </sheetData>
